--- a/artfynd/A 3372-2024 artfynd.xlsx
+++ b/artfynd/A 3372-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2647,6 +2647,120 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114667628</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78937</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Megalaria grossa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>kallings, Skogs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>700140</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6384412</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Träkumla</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elina  Ambjörnsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elina  Ambjörnsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3372-2024 artfynd.xlsx
+++ b/artfynd/A 3372-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
